--- a/output/北塩原村_村HP3分野の棚卸し.xlsx
+++ b/output/北塩原村_村HP3分野の棚卸し.xlsx
@@ -660,7 +660,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>当方の環境からは403で取得できない。村での確認をお願いする。</t>
+          <t>当方の環境からは403で取得できない。出所はレビューの記述である。このほか、令和8年10月10日のRed Teamレビューが医療機関・相談・救急情報、防災、AED設置施設、通行止め情報の4ページを確認している（北塩原村_RedTeam_救急防災冬季.xlsx 08シート）。</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3066,6 +3066,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>No.6・No.8・No.12（救急・防災・冬季）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>村HPの他のページ</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>医療機関・相談・救急情報、防災、AED設置施設、通行止め情報の4ページは、令和8年10月10日のRed Teamレビューで別に扱った（北塩原村_RedTeam_救急防災冬季.xlsx 07シート）</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ＲＴ-1・ＲＴ-2・ＲＴ-5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
